--- a/students.xlsx
+++ b/students.xlsx
@@ -12,14 +12,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="21">
   <si>
     <t>Company name</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -51,6 +48,33 @@
   </si>
   <si>
     <t>asdas</t>
+  </si>
+  <si>
+    <t>Driver Files</t>
+  </si>
+  <si>
+    <t>Berran Test</t>
+  </si>
+  <si>
+    <t>CDL</t>
+  </si>
+  <si>
+    <t>MEDICAL_CERT</t>
+  </si>
+  <si>
+    <t>MVR</t>
+  </si>
+  <si>
+    <t>CLEARING_HOUSE</t>
+  </si>
+  <si>
+    <t>SSN</t>
+  </si>
+  <si>
+    <t>DRIVER_APPLICATION</t>
+  </si>
+  <si>
+    <t>PEV</t>
   </si>
 </sst>
 </file>
@@ -58,7 +82,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -66,16 +90,55 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="darkGray"/>
     </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill>
+        <fgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill>
+        <fgColor indexed="64"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -83,129 +146,571 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin"/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom>
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <top style="thin"/>
+      <bottom>
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right>
+        <color indexed="8"/>
+      </right>
+      <top style="thin"/>
+      <bottom>
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right>
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom>
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right>
+        <color indexed="8"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right>
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right>
+        <color indexed="8"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right>
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="0" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="0" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="22" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="0" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="0" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="31.25" customWidth="true"/>
+    <col min="2" max="2" width="23.4375" customWidth="true"/>
+    <col min="3" max="3" width="15.625" customWidth="true"/>
+    <col min="4" max="4" width="11.71875" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s" s="3">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s" s="3">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s" s="3">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3">
+      <c r="C3" t="s" s="0">
         <v>5</v>
       </c>
-    </row>
-    <row r="3">
       <c r="D3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="E3" t="s" s="0">
+    </row>
+    <row r="4">
+      <c r="C4" t="s" s="0">
         <v>7</v>
       </c>
-    </row>
-    <row r="4">
       <c r="D4" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="E4" t="s" s="0">
+      <c r="D5" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="3">
+        <v>11</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9">
+      <c r="C9" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="s" s="0">
         <v>7</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="D5" t="s" s="0">
+      <c r="D10" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="E5" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="D6" t="s" s="0">
+      <c r="D12" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="E6" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="D7" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
+      <c r="D13" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="D9" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="D10" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="D11" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="D12" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="E12" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="D13" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="E13" t="s" s="0">
-        <v>7</v>
+      <c r="C14" s="6"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15">
+      <c r="B15" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B14:D14"/>
+  </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>